--- a/capstoneproject/src/test/resources/TestData1.xlsx
+++ b/capstoneproject/src/test/resources/TestData1.xlsx
@@ -3,38 +3,26 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TAPABRATA\Desktop\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72E5A30D-59F2-4118-A26B-FEA8EC40269A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{DD9C164B-C39F-4E85-B97F-230CFD3A4357}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9768" yWindow="1596" windowWidth="9936" windowHeight="10524" xr2:uid="{17DF77DB-491B-4C56-837B-3CD32A7CB8CC}"/>
+    <workbookView xWindow="11436" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{17DF77DB-491B-4C56-837B-3CD32A7CB8CC}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="0"/>
+  <oleSize ref="A1:G17"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="8">
   <si>
     <t>Username</t>
   </si>
@@ -48,10 +36,16 @@
     <t>problem_user</t>
   </si>
   <si>
+    <t>secret_sauce</t>
+  </si>
+  <si>
+    <t>invalid_user</t>
+  </si>
+  <si>
+    <t>wrong_password</t>
+  </si>
+  <si>
     <t>performance_glitch_user</t>
-  </si>
-  <si>
-    <t>secret_sauce</t>
   </si>
 </sst>
 </file>
@@ -403,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{97AF94B2-FF1F-48D1-BBC1-5A1D6B355472}">
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.6640625" bestFit="1" customWidth="1"/>
@@ -423,7 +417,7 @@
         <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
@@ -431,15 +425,46 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" t="s">
         <v>4</v>
       </c>
-      <c r="B4" t="s">
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3"/>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86B48F3C-3171-4882-99B8-F848AF62ABE8}">
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
         <v>5</v>
+      </c>
+      <c r="B2" t="s">
+        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/capstoneproject/src/test/resources/TestData1.xlsx
+++ b/capstoneproject/src/test/resources/TestData1.xlsx
@@ -3,16 +3,17 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{DD9C164B-C39F-4E85-B97F-230CFD3A4357}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{9213BAA0-B9DB-4CDB-9234-861F6A92C08E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11436" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{17DF77DB-491B-4C56-837B-3CD32A7CB8CC}"/>
+    <workbookView xWindow="11436" yWindow="0" windowWidth="11712" windowHeight="12336" activeTab="1" xr2:uid="{17DF77DB-491B-4C56-837B-3CD32A7CB8CC}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet3" sheetId="3" r:id="rId2"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId3"/>
   </sheets>
   <calcPr calcId="0"/>
-  <oleSize ref="A1:G17"/>
+  <oleSize ref="A1:H15"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -22,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="14">
   <si>
     <t>Username</t>
   </si>
@@ -46,6 +47,24 @@
   </si>
   <si>
     <t>performance_glitch_user</t>
+  </si>
+  <si>
+    <t>ProductName</t>
+  </si>
+  <si>
+    <t>Category</t>
+  </si>
+  <si>
+    <t>Sauce Labs Backpack</t>
+  </si>
+  <si>
+    <t>Apparel</t>
+  </si>
+  <si>
+    <t>Sauce Labs Bike Light</t>
+  </si>
+  <si>
+    <t>Accessories</t>
   </si>
 </sst>
 </file>
@@ -443,6 +462,40 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC5F7B09-1482-4DD8-9AC3-09BA3A229BFD}">
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86B48F3C-3171-4882-99B8-F848AF62ABE8}">
   <dimension ref="A1:B2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
